--- a/ITI/DeId/StructureDefinition-IHE.BasicAudit.DeIdentification.Source.xlsx
+++ b/ITI/DeId/StructureDefinition-IHE.BasicAudit.DeIdentification.Source.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-comment</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:54:51-05:00</t>
+    <t>2026-10-17T19:18:20-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
